--- a/backend/signal_logs/2026-09-04/signals_2026-09-04.xlsx
+++ b/backend/signal_logs/2026-09-04/signals_2026-09-04.xlsx
@@ -810,6 +810,11 @@
           <t>NSE:ANGELONE26SEP300PE</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Closed flat ~9.6 (+0.0% from entry, EOD estimate)</t>
+        </is>
+      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -921,6 +926,11 @@
           <t>NSE:HAVELLS26SEP1160PE</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Closed down ~35.9 (-2.5% from entry, EOD estimate)</t>
+        </is>
+      </c>
       <c r="AD9" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1159,6 +1169,11 @@
           <t>NSE:HYUNDAI26SEP2200CE</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Closed down ~56.5 (-12.5% from entry, EOD estimate)</t>
+        </is>
+      </c>
       <c r="AD11" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1270,6 +1285,11 @@
           <t>NSE:KEI26SEP4900PE</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Closed up ~185.5 (+0.8% from entry, EOD estimate)</t>
+        </is>
+      </c>
       <c r="AD12" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1889,6 +1909,11 @@
           <t>NSE:HINDZINC26SEP600CE</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Closed down ~18.65 (-0.5% from entry, EOD estimate)</t>
+        </is>
+      </c>
       <c r="AD17" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -1998,6 +2023,11 @@
       <c r="W18" t="inlineStr">
         <is>
           <t>NSE:JINDALSTEL26SEP1160CE</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Closed down ~31.75 (-8.0% from entry, EOD estimate)</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">

--- a/backend/signal_logs/2026-09-04/signals_2026-09-04.xlsx
+++ b/backend/signal_logs/2026-09-04/signals_2026-09-04.xlsx
@@ -810,9 +810,14 @@
           <t>NSE:ANGELONE26SEP300PE</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2026-09-07 09:38:00</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Closed flat ~9.6 (+0.0% from entry, EOD estimate)</t>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
@@ -926,9 +931,19 @@
           <t>NSE:HAVELLS26SEP1160PE</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-08 09:22:00</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-09-09 12:00:00</t>
+        </is>
+      </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Closed down ~35.9 (-2.5% from entry, EOD estimate)</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -1042,9 +1057,14 @@
           <t>NSE:LICHSGFIN26SEP570CE</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:06:00</t>
+        </is>
+      </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1169,9 +1189,14 @@
           <t>NSE:HYUNDAI26SEP2200CE</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:15:00</t>
+        </is>
+      </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Closed down ~56.5 (-12.5% from entry, EOD estimate)</t>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
@@ -1285,9 +1310,24 @@
           <t>NSE:KEI26SEP4900PE</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-07 09:29:00</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>2026-09-07 11:35:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-09 10:00:00</t>
+        </is>
+      </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Closed up ~185.5 (+0.8% from entry, EOD estimate)</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
@@ -1528,9 +1568,24 @@
           <t>NSE:PAYTM26SEP1660CE</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:16:00</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:21:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-09 09:25:00</t>
+        </is>
+      </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -1655,9 +1710,14 @@
           <t>NSE:JINDALSTEL26SEP1160CE</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2026-09-07 09:18:00</t>
+        </is>
+      </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -1782,9 +1842,24 @@
           <t>NSE:MCX26SEP3250CE</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-07 09:15:00</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>2026-09-07 09:22:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-07 12:06:00</t>
+        </is>
+      </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>Target 3 Hit</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -1909,11 +1984,7 @@
           <t>NSE:HINDZINC26SEP600CE</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Closed down ~18.65 (-0.5% from entry, EOD estimate)</t>
-        </is>
-      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
@@ -2025,9 +2096,14 @@
           <t>NSE:JINDALSTEL26SEP1160CE</t>
         </is>
       </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>2026-09-07 09:18:00</t>
+        </is>
+      </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>Closed down ~31.75 (-8.0% from entry, EOD estimate)</t>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr">

--- a/backend/signal_logs/2026-09-04/signals_2026-09-04.xlsx
+++ b/backend/signal_logs/2026-09-04/signals_2026-09-04.xlsx
@@ -1441,9 +1441,14 @@
           <t>NSE:HINDZINC26SEP600CE</t>
         </is>
       </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Expired (no SL/Target hit)</t>
+          <t>SL Hit</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -1984,7 +1989,16 @@
           <t>NSE:HINDZINC26SEP600CE</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2026-09-11 09:15:00</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AD17" t="inlineStr">
         <is>
           <t>v1 (2026-09-02)</t>
